--- a/frontend/tests/fixtures/report.xlsx
+++ b/frontend/tests/fixtures/report.xlsx
@@ -9,8 +9,9 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SLIDE_1" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SLIDE_2 panel" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Hidden data" sheetId="3" state="hidden" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Numbers" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SLIDE_3 pair" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Hidden data" sheetId="4" state="hidden" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Numbers" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,16 +20,17 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="9">
+  <numFmts count="10">
     <numFmt numFmtId="164" formatCode="+0.0;-0.0;0.0"/>
     <numFmt numFmtId="165" formatCode="#,##0.0,,&quot; m&quot;"/>
     <numFmt numFmtId="166" formatCode="0.0%"/>
     <numFmt numFmtId="167" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="168" formatCode="dd/mm/yyyy"/>
-    <numFmt numFmtId="169" formatCode="dd mmm yyyy hh:mm AM/PM"/>
-    <numFmt numFmtId="170" formatCode="[$-410]mmmm yyyy"/>
-    <numFmt numFmtId="171" formatCode="#,##0 [$€-410]"/>
-    <numFmt numFmtId="172" formatCode="0;[Red]-0"/>
+    <numFmt numFmtId="169" formatCode="#,##0.0"/>
+    <numFmt numFmtId="170" formatCode="dd mmm yyyy hh:mm AM/PM"/>
+    <numFmt numFmtId="171" formatCode="[$-410]mmmm yyyy"/>
+    <numFmt numFmtId="172" formatCode="#,##0 [$€-410]"/>
+    <numFmt numFmtId="173" formatCode="0;[Red]-0"/>
   </numFmts>
   <fonts count="6">
     <font>
@@ -115,7 +117,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -135,13 +137,14 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="12" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="170" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="171" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="172" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="173" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -1135,13 +1138,293 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:L14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="9" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="15" customWidth="1" min="11" max="11"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>secret</t>
+          <t>Loans vs deposits by region</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Region</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Q1</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>Q2</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>Region</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>Q1</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>Q2</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>Q3</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="D5" s="17" t="n">
+        <v>-101.25</v>
+      </c>
+      <c r="E5" s="17" t="n">
+        <v>-90</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="I5" s="17" t="n">
+        <v>-101.25</v>
+      </c>
+      <c r="J5" s="17" t="n">
+        <v>-90</v>
+      </c>
+      <c r="K5" s="17" t="n">
+        <v>-78.75</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="D6" s="17" t="n">
+        <v>-63.75</v>
+      </c>
+      <c r="E6" s="17" t="n">
+        <v>-52.5</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="I6" s="17" t="n">
+        <v>-63.75</v>
+      </c>
+      <c r="J6" s="17" t="n">
+        <v>-52.5</v>
+      </c>
+      <c r="K6" s="17" t="n">
+        <v>-41.25</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>R3</t>
+        </is>
+      </c>
+      <c r="D7" s="17" t="n">
+        <v>-26.25</v>
+      </c>
+      <c r="E7" s="17" t="n">
+        <v>-15</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>R3</t>
+        </is>
+      </c>
+      <c r="I7" s="17" t="n">
+        <v>-26.25</v>
+      </c>
+      <c r="J7" s="17" t="n">
+        <v>-15</v>
+      </c>
+      <c r="K7" s="17" t="n">
+        <v>-3.75</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>R4</t>
+        </is>
+      </c>
+      <c r="D8" s="17" t="n">
+        <v>11.25</v>
+      </c>
+      <c r="E8" s="17" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>R4</t>
+        </is>
+      </c>
+      <c r="I8" s="17" t="n">
+        <v>11.25</v>
+      </c>
+      <c r="J8" s="17" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="K8" s="17" t="n">
+        <v>33.75</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>R5</t>
+        </is>
+      </c>
+      <c r="D9" s="17" t="n">
+        <v>48.75</v>
+      </c>
+      <c r="E9" s="17" t="n">
+        <v>60</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>R5</t>
+        </is>
+      </c>
+      <c r="I9" s="17" t="n">
+        <v>48.75</v>
+      </c>
+      <c r="J9" s="17" t="n">
+        <v>60</v>
+      </c>
+      <c r="K9" s="17" t="n">
+        <v>71.25</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>R6</t>
+        </is>
+      </c>
+      <c r="D10" s="17" t="n">
+        <v>86.25</v>
+      </c>
+      <c r="E10" s="17" t="n">
+        <v>97.5</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>R6</t>
+        </is>
+      </c>
+      <c r="I10" s="17" t="n">
+        <v>86.25</v>
+      </c>
+      <c r="J10" s="17" t="n">
+        <v>97.5</v>
+      </c>
+      <c r="K10" s="17" t="n">
+        <v>108.75</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>R7</t>
+        </is>
+      </c>
+      <c r="I11" s="17" t="n">
+        <v>123.75</v>
+      </c>
+      <c r="J11" s="17" t="n">
+        <v>135</v>
+      </c>
+      <c r="K11" s="17" t="n">
+        <v>146.25</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>R8</t>
+        </is>
+      </c>
+      <c r="I12" s="17" t="n">
+        <v>161.25</v>
+      </c>
+      <c r="J12" s="17" t="n">
+        <v>172.5</v>
+      </c>
+      <c r="K12" s="17" t="n">
+        <v>183.75</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>R9</t>
+        </is>
+      </c>
+      <c r="I13" s="17" t="n">
+        <v>198.75</v>
+      </c>
+      <c r="J13" s="17" t="n">
+        <v>210</v>
+      </c>
+      <c r="K13" s="17" t="n">
+        <v>221.25</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>x</t>
         </is>
       </c>
     </row>
@@ -1156,21 +1439,42 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:A1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>secret</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="B2:B11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="2">
-      <c r="B2" s="17" t="n">
+      <c r="B2" s="18" t="n">
         <v>1234.5</v>
       </c>
     </row>
     <row r="3">
-      <c r="B3" s="18" t="n">
+      <c r="B3" s="19" t="n">
         <v>0.000123</v>
       </c>
     </row>
     <row r="4">
-      <c r="B4" s="19" t="n">
+      <c r="B4" s="20" t="n">
         <v>1.5</v>
       </c>
     </row>
@@ -1185,27 +1489,27 @@
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="20" t="n">
+      <c r="B7" s="21" t="n">
         <v>45000.75</v>
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="21" t="n">
+      <c r="B8" s="22" t="n">
         <v>45000</v>
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="22" t="n">
+      <c r="B9" s="23" t="n">
         <v>1234.5</v>
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="23" t="n">
+      <c r="B10" s="24" t="n">
         <v>-5</v>
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="24" t="n">
+      <c r="B11" s="25" t="n">
         <v>0.25</v>
       </c>
     </row>
